--- a/artfynd/A 47136-2021 artfynd.xlsx
+++ b/artfynd/A 47136-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129186468</v>
       </c>
       <c r="B2" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47136-2021 artfynd.xlsx
+++ b/artfynd/A 47136-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129186468</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47136-2021 artfynd.xlsx
+++ b/artfynd/A 47136-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129186468</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47136-2021 artfynd.xlsx
+++ b/artfynd/A 47136-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129186468</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47136-2021 artfynd.xlsx
+++ b/artfynd/A 47136-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129186468</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47136-2021 artfynd.xlsx
+++ b/artfynd/A 47136-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129186468</v>
       </c>
       <c r="B2" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47136-2021 artfynd.xlsx
+++ b/artfynd/A 47136-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129186468</v>
       </c>
       <c r="B2" t="n">
-        <v>91587</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2089807</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>(11G6b01), Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>551849</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6628765</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1995-07-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1995-07-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>110661011 / LEP SATU / Enstaka-sparsam (1)  / OBJ.AREA:4,7 ha</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Gullberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
